--- a/docs/CodeSystem-tiltakstatus-nesteundersokelse-cs.xlsx
+++ b/docs/CodeSystem-tiltakstatus-nesteundersokelse-cs.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Verdisett for tiltaksstatus neste undersøkelse</t>
+    <t>Next Step After Grading</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-08T17:39:22+01:00</t>
+    <t>2025-11-11T17:38:50+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Verdisett som beskriver verdier for forløpsstatus for neste undersøkelse for Retinascreening</t>
+    <t>Valueset describing next step in the screening process after grading. (3000-series)</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/CodeSystem-tiltakstatus-nesteundersokelse-cs.xlsx
+++ b/docs/CodeSystem-tiltakstatus-nesteundersokelse-cs.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Next Step After Grading</t>
+    <t>Next Examination</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-11T17:38:50+01:00</t>
+    <t>2025-11-12T18:21:01+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Valueset describing next step in the screening process after grading. (3000-series)</t>
+    <t>Next step for this patient is a new examination. (3000-series)</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/CodeSystem-tiltakstatus-nesteundersokelse-cs.xlsx
+++ b/docs/CodeSystem-tiltakstatus-nesteundersokelse-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-12T18:21:01+01:00</t>
+    <t>2025-11-13T17:39:30+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-tiltakstatus-nesteundersokelse-cs.xlsx
+++ b/docs/CodeSystem-tiltakstatus-nesteundersokelse-cs.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Next Step After Grading</t>
+    <t>Next Examination</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-11T17:38:50+01:00</t>
+    <t>2025-11-15T17:14:08+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Valueset describing next step in the screening process after grading. (3000-series)</t>
+    <t>Next step for this patient is a new examination. (3000-series)</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/CodeSystem-tiltakstatus-nesteundersokelse-cs.xlsx
+++ b/docs/CodeSystem-tiltakstatus-nesteundersokelse-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-15T17:14:08+01:00</t>
+    <t>2025-11-16T16:39:43+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
